--- a/templates/3D/sust yield server/setup.xlsx
+++ b/templates/3D/sust yield server/setup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7969EB1-2877-467B-B226-29ECA8BC9604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B641C5A-12B4-4CA8-9971-CE19F5130DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grid" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2649" uniqueCount="1216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2651" uniqueCount="1217">
   <si>
     <t>nlay</t>
   </si>
@@ -3695,6 +3695,9 @@
   </si>
   <si>
     <t>12_99_130</t>
+  </si>
+  <si>
+    <t>qv_11</t>
   </si>
 </sst>
 </file>
@@ -4221,7 +4224,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="8" width="10.73046875" bestFit="1" customWidth="1"/>
@@ -4229,7 +4232,7 @@
     <col min="12" max="12" width="11.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>89</v>
       </c>
@@ -4239,35 +4242,38 @@
       <c r="C1" t="s">
         <v>114</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M1" s="11" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>91</v>
       </c>
@@ -4290,22 +4296,25 @@
         <v>-10000</v>
       </c>
       <c r="H2" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I2" s="11">
         <v>-50000</v>
       </c>
-      <c r="I2" s="11">
+      <c r="J2" s="11">
         <v>-100000</v>
       </c>
-      <c r="J2" s="11">
+      <c r="K2" s="11">
         <v>-200000</v>
       </c>
-      <c r="K2" s="11">
+      <c r="L2" s="11">
         <v>-500000</v>
       </c>
-      <c r="L2" s="11">
+      <c r="M2" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>92</v>
       </c>
@@ -4328,22 +4337,25 @@
         <v>-10000</v>
       </c>
       <c r="H3" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I3" s="11">
         <v>-50000</v>
       </c>
-      <c r="I3" s="11">
+      <c r="J3" s="11">
         <v>-100000</v>
       </c>
-      <c r="J3" s="11">
+      <c r="K3" s="11">
         <v>-200000</v>
       </c>
-      <c r="K3" s="11">
+      <c r="L3" s="11">
         <v>-500000</v>
       </c>
-      <c r="L3" s="11">
+      <c r="M3" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>93</v>
       </c>
@@ -4366,22 +4378,25 @@
         <v>-10000</v>
       </c>
       <c r="H4" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I4" s="11">
         <v>-50000</v>
       </c>
-      <c r="I4" s="11">
+      <c r="J4" s="11">
         <v>-100000</v>
       </c>
-      <c r="J4" s="11">
+      <c r="K4" s="11">
         <v>-200000</v>
       </c>
-      <c r="K4" s="11">
+      <c r="L4" s="11">
         <v>-500000</v>
       </c>
-      <c r="L4" s="11">
+      <c r="M4" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>94</v>
       </c>
@@ -4404,22 +4419,25 @@
         <v>-10000</v>
       </c>
       <c r="H5" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I5" s="11">
         <v>-50000</v>
       </c>
-      <c r="I5" s="11">
+      <c r="J5" s="11">
         <v>-100000</v>
       </c>
-      <c r="J5" s="11">
+      <c r="K5" s="11">
         <v>-200000</v>
       </c>
-      <c r="K5" s="11">
+      <c r="L5" s="11">
         <v>-500000</v>
       </c>
-      <c r="L5" s="11">
+      <c r="M5" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>95</v>
       </c>
@@ -4442,22 +4460,25 @@
         <v>-10000</v>
       </c>
       <c r="H6" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I6" s="11">
         <v>-50000</v>
       </c>
-      <c r="I6" s="11">
+      <c r="J6" s="11">
         <v>-100000</v>
       </c>
-      <c r="J6" s="11">
+      <c r="K6" s="11">
         <v>-200000</v>
       </c>
-      <c r="K6" s="11">
+      <c r="L6" s="11">
         <v>-500000</v>
       </c>
-      <c r="L6" s="11">
+      <c r="M6" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7" s="11" t="s">
         <v>147</v>
       </c>
@@ -4480,22 +4501,25 @@
         <v>-10000</v>
       </c>
       <c r="H7" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I7" s="11">
         <v>-50000</v>
       </c>
-      <c r="I7" s="11">
+      <c r="J7" s="11">
         <v>-100000</v>
       </c>
-      <c r="J7" s="11">
+      <c r="K7" s="11">
         <v>-200000</v>
       </c>
-      <c r="K7" s="11">
+      <c r="L7" s="11">
         <v>-500000</v>
       </c>
-      <c r="L7" s="11">
+      <c r="M7" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A8" s="11" t="s">
         <v>398</v>
       </c>
@@ -4518,22 +4542,25 @@
         <v>-10000</v>
       </c>
       <c r="H8" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I8" s="11">
         <v>-50000</v>
       </c>
-      <c r="I8" s="11">
+      <c r="J8" s="11">
         <v>-100000</v>
       </c>
-      <c r="J8" s="11">
+      <c r="K8" s="11">
         <v>-200000</v>
       </c>
-      <c r="K8" s="11">
+      <c r="L8" s="11">
         <v>-500000</v>
       </c>
-      <c r="L8" s="11">
+      <c r="M8" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A9" s="11" t="s">
         <v>399</v>
       </c>
@@ -4556,22 +4583,25 @@
         <v>-10000</v>
       </c>
       <c r="H9" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I9" s="11">
         <v>-50000</v>
       </c>
-      <c r="I9" s="11">
+      <c r="J9" s="11">
         <v>-100000</v>
       </c>
-      <c r="J9" s="11">
+      <c r="K9" s="11">
         <v>-200000</v>
       </c>
-      <c r="K9" s="11">
+      <c r="L9" s="11">
         <v>-500000</v>
       </c>
-      <c r="L9" s="11">
+      <c r="M9" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A10" s="11" t="s">
         <v>400</v>
       </c>
@@ -4594,22 +4624,25 @@
         <v>-10000</v>
       </c>
       <c r="H10" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I10" s="11">
         <v>-50000</v>
       </c>
-      <c r="I10" s="11">
+      <c r="J10" s="11">
         <v>-100000</v>
       </c>
-      <c r="J10" s="11">
+      <c r="K10" s="11">
         <v>-200000</v>
       </c>
-      <c r="K10" s="11">
+      <c r="L10" s="11">
         <v>-500000</v>
       </c>
-      <c r="L10" s="11">
+      <c r="M10" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A11" s="11" t="s">
         <v>401</v>
       </c>
@@ -4632,22 +4665,25 @@
         <v>-10000</v>
       </c>
       <c r="H11" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I11" s="11">
         <v>-50000</v>
       </c>
-      <c r="I11" s="11">
+      <c r="J11" s="11">
         <v>-100000</v>
       </c>
-      <c r="J11" s="11">
+      <c r="K11" s="11">
         <v>-200000</v>
       </c>
-      <c r="K11" s="11">
+      <c r="L11" s="11">
         <v>-500000</v>
       </c>
-      <c r="L11" s="11">
+      <c r="M11" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A12" s="11" t="s">
         <v>402</v>
       </c>
@@ -4670,22 +4706,25 @@
         <v>-10000</v>
       </c>
       <c r="H12" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I12" s="11">
         <v>-50000</v>
       </c>
-      <c r="I12" s="11">
+      <c r="J12" s="11">
         <v>-100000</v>
       </c>
-      <c r="J12" s="11">
+      <c r="K12" s="11">
         <v>-200000</v>
       </c>
-      <c r="K12" s="11">
+      <c r="L12" s="11">
         <v>-500000</v>
       </c>
-      <c r="L12" s="11">
+      <c r="M12" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A13" s="11" t="s">
         <v>403</v>
       </c>
@@ -4708,22 +4747,25 @@
         <v>-10000</v>
       </c>
       <c r="H13" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I13" s="11">
         <v>-50000</v>
       </c>
-      <c r="I13" s="11">
+      <c r="J13" s="11">
         <v>-100000</v>
       </c>
-      <c r="J13" s="11">
+      <c r="K13" s="11">
         <v>-200000</v>
       </c>
-      <c r="K13" s="11">
+      <c r="L13" s="11">
         <v>-500000</v>
       </c>
-      <c r="L13" s="11">
+      <c r="M13" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A14" s="11" t="s">
         <v>404</v>
       </c>
@@ -4746,22 +4788,25 @@
         <v>-10000</v>
       </c>
       <c r="H14" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I14" s="11">
         <v>-50000</v>
       </c>
-      <c r="I14" s="11">
+      <c r="J14" s="11">
         <v>-100000</v>
       </c>
-      <c r="J14" s="11">
+      <c r="K14" s="11">
         <v>-200000</v>
       </c>
-      <c r="K14" s="11">
+      <c r="L14" s="11">
         <v>-500000</v>
       </c>
-      <c r="L14" s="11">
+      <c r="M14" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A15" s="11" t="s">
         <v>405</v>
       </c>
@@ -4784,22 +4829,25 @@
         <v>-10000</v>
       </c>
       <c r="H15" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I15" s="11">
         <v>-50000</v>
       </c>
-      <c r="I15" s="11">
+      <c r="J15" s="11">
         <v>-100000</v>
       </c>
-      <c r="J15" s="11">
+      <c r="K15" s="11">
         <v>-200000</v>
       </c>
-      <c r="K15" s="11">
+      <c r="L15" s="11">
         <v>-500000</v>
       </c>
-      <c r="L15" s="11">
+      <c r="M15" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A16" s="11" t="s">
         <v>406</v>
       </c>
@@ -4822,18 +4870,21 @@
         <v>-10000</v>
       </c>
       <c r="H16" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I16" s="11">
         <v>-50000</v>
       </c>
-      <c r="I16" s="11">
+      <c r="J16" s="11">
         <v>-100000</v>
       </c>
-      <c r="J16" s="11">
+      <c r="K16" s="11">
         <v>-200000</v>
       </c>
-      <c r="K16" s="11">
+      <c r="L16" s="11">
         <v>-500000</v>
       </c>
-      <c r="L16" s="11">
+      <c r="M16" s="11">
         <v>-1000000</v>
       </c>
     </row>
@@ -4870,16 +4921,17 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AD51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="12.265625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.9296875" style="11" customWidth="1"/>
     <col min="6" max="6" width="10.59765625" style="11" customWidth="1"/>
-    <col min="10" max="10" width="10.9296875" style="11" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" style="11"/>
+    <col min="11" max="11" width="10.9296875" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A1" s="11" t="s">
         <v>89</v>
       </c>
@@ -4919,8 +4971,11 @@
       <c r="M1" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="N1" s="11" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A2" s="11" t="s">
         <v>91</v>
       </c>
@@ -4960,7 +5015,9 @@
       <c r="M2" s="11">
         <v>0</v>
       </c>
-      <c r="P2" s="11"/>
+      <c r="N2" s="11">
+        <v>0</v>
+      </c>
       <c r="Q2" s="11"/>
       <c r="R2" s="11"/>
       <c r="S2" s="11"/>
@@ -4973,8 +5030,9 @@
       <c r="Z2" s="11"/>
       <c r="AA2" s="11"/>
       <c r="AB2" s="11"/>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC2" s="11"/>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A3" s="11" t="s">
         <v>91</v>
       </c>
@@ -5000,21 +5058,23 @@
         <v>-10000</v>
       </c>
       <c r="I3" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J3" s="11">
         <v>-50000</v>
       </c>
-      <c r="J3" s="11">
+      <c r="K3" s="11">
         <v>-100000</v>
       </c>
-      <c r="K3" s="11">
+      <c r="L3" s="11">
         <v>-200000</v>
       </c>
-      <c r="L3" s="11">
+      <c r="M3" s="11">
         <v>-500000</v>
       </c>
-      <c r="M3" s="11">
+      <c r="N3" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O3" s="11"/>
       <c r="P3" s="11"/>
       <c r="Q3" s="11"/>
       <c r="R3" s="11"/>
@@ -5028,8 +5088,9 @@
       <c r="Z3" s="11"/>
       <c r="AA3" s="11"/>
       <c r="AB3" s="11"/>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC3" s="11"/>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A4" s="11" t="s">
         <v>91</v>
       </c>
@@ -5055,21 +5116,23 @@
         <v>-10000</v>
       </c>
       <c r="I4" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J4" s="11">
         <v>-50000</v>
       </c>
-      <c r="J4" s="11">
+      <c r="K4" s="11">
         <v>-100000</v>
       </c>
-      <c r="K4" s="11">
+      <c r="L4" s="11">
         <v>-200000</v>
       </c>
-      <c r="L4" s="11">
+      <c r="M4" s="11">
         <v>-500000</v>
       </c>
-      <c r="M4" s="11">
+      <c r="N4" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O4" s="11"/>
       <c r="P4" s="11"/>
       <c r="Q4" s="11"/>
       <c r="R4" s="11"/>
@@ -5083,8 +5146,9 @@
       <c r="Z4" s="11"/>
       <c r="AA4" s="11"/>
       <c r="AB4" s="11"/>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC4" s="11"/>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A5" s="11" t="s">
         <v>92</v>
       </c>
@@ -5124,7 +5188,9 @@
       <c r="M5" s="11">
         <v>0</v>
       </c>
-      <c r="O5" s="11"/>
+      <c r="N5" s="11">
+        <v>0</v>
+      </c>
       <c r="P5" s="11"/>
       <c r="Q5" s="11"/>
       <c r="R5" s="11"/>
@@ -5138,8 +5204,9 @@
       <c r="Z5" s="11"/>
       <c r="AA5" s="11"/>
       <c r="AB5" s="11"/>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC5" s="11"/>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A6" s="11" t="s">
         <v>92</v>
       </c>
@@ -5165,21 +5232,23 @@
         <v>-10000</v>
       </c>
       <c r="I6" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J6" s="11">
         <v>-50000</v>
       </c>
-      <c r="J6" s="11">
+      <c r="K6" s="11">
         <v>-100000</v>
       </c>
-      <c r="K6" s="11">
+      <c r="L6" s="11">
         <v>-200000</v>
       </c>
-      <c r="L6" s="11">
+      <c r="M6" s="11">
         <v>-500000</v>
       </c>
-      <c r="M6" s="11">
+      <c r="N6" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O6" s="11"/>
       <c r="P6" s="11"/>
       <c r="Q6" s="11"/>
       <c r="R6" s="11"/>
@@ -5193,8 +5262,9 @@
       <c r="Z6" s="11"/>
       <c r="AA6" s="11"/>
       <c r="AB6" s="11"/>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC6" s="11"/>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A7" s="11" t="s">
         <v>92</v>
       </c>
@@ -5220,21 +5290,23 @@
         <v>-10000</v>
       </c>
       <c r="I7" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J7" s="11">
         <v>-50000</v>
       </c>
-      <c r="J7" s="11">
+      <c r="K7" s="11">
         <v>-100000</v>
       </c>
-      <c r="K7" s="11">
+      <c r="L7" s="11">
         <v>-200000</v>
       </c>
-      <c r="L7" s="11">
+      <c r="M7" s="11">
         <v>-500000</v>
       </c>
-      <c r="M7" s="11">
+      <c r="N7" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O7" s="11"/>
       <c r="P7" s="11"/>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
@@ -5248,8 +5320,9 @@
       <c r="Z7" s="11"/>
       <c r="AA7" s="11"/>
       <c r="AB7" s="11"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC7" s="11"/>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A8" s="11" t="s">
         <v>93</v>
       </c>
@@ -5289,7 +5362,9 @@
       <c r="M8" s="11">
         <v>0</v>
       </c>
-      <c r="O8" s="11"/>
+      <c r="N8" s="11">
+        <v>0</v>
+      </c>
       <c r="P8" s="11"/>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
@@ -5303,8 +5378,9 @@
       <c r="Z8" s="11"/>
       <c r="AA8" s="11"/>
       <c r="AB8" s="11"/>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC8" s="11"/>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A9" s="11" t="s">
         <v>93</v>
       </c>
@@ -5330,21 +5406,23 @@
         <v>-10000</v>
       </c>
       <c r="I9" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J9" s="11">
         <v>-50000</v>
       </c>
-      <c r="J9" s="11">
+      <c r="K9" s="11">
         <v>-100000</v>
       </c>
-      <c r="K9" s="11">
+      <c r="L9" s="11">
         <v>-200000</v>
       </c>
-      <c r="L9" s="11">
+      <c r="M9" s="11">
         <v>-500000</v>
       </c>
-      <c r="M9" s="11">
+      <c r="N9" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O9" s="11"/>
       <c r="P9" s="11"/>
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
@@ -5358,8 +5436,9 @@
       <c r="Z9" s="11"/>
       <c r="AA9" s="11"/>
       <c r="AB9" s="11"/>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC9" s="11"/>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A10" s="11" t="s">
         <v>93</v>
       </c>
@@ -5385,21 +5464,23 @@
         <v>-10000</v>
       </c>
       <c r="I10" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J10" s="11">
         <v>-50000</v>
       </c>
-      <c r="J10" s="11">
+      <c r="K10" s="11">
         <v>-100000</v>
       </c>
-      <c r="K10" s="11">
+      <c r="L10" s="11">
         <v>-200000</v>
       </c>
-      <c r="L10" s="11">
+      <c r="M10" s="11">
         <v>-500000</v>
       </c>
-      <c r="M10" s="11">
+      <c r="N10" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O10" s="11"/>
       <c r="P10" s="11"/>
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
@@ -5413,8 +5494,9 @@
       <c r="Z10" s="11"/>
       <c r="AA10" s="11"/>
       <c r="AB10" s="11"/>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC10" s="11"/>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A11" s="11" t="s">
         <v>94</v>
       </c>
@@ -5454,7 +5536,9 @@
       <c r="M11" s="11">
         <v>0</v>
       </c>
-      <c r="O11" s="11"/>
+      <c r="N11" s="11">
+        <v>0</v>
+      </c>
       <c r="P11" s="11"/>
       <c r="Q11" s="11"/>
       <c r="R11" s="11"/>
@@ -5468,8 +5552,9 @@
       <c r="Z11" s="11"/>
       <c r="AA11" s="11"/>
       <c r="AB11" s="11"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC11" s="11"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A12" s="11" t="s">
         <v>94</v>
       </c>
@@ -5495,21 +5580,23 @@
         <v>-10000</v>
       </c>
       <c r="I12" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J12" s="11">
         <v>-50000</v>
       </c>
-      <c r="J12" s="11">
+      <c r="K12" s="11">
         <v>-100000</v>
       </c>
-      <c r="K12" s="11">
+      <c r="L12" s="11">
         <v>-200000</v>
       </c>
-      <c r="L12" s="11">
+      <c r="M12" s="11">
         <v>-500000</v>
       </c>
-      <c r="M12" s="11">
+      <c r="N12" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O12" s="11"/>
       <c r="P12" s="11"/>
       <c r="Q12" s="11"/>
       <c r="R12" s="11"/>
@@ -5523,8 +5610,9 @@
       <c r="Z12" s="11"/>
       <c r="AA12" s="11"/>
       <c r="AB12" s="11"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC12" s="11"/>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A13" s="11" t="s">
         <v>94</v>
       </c>
@@ -5550,21 +5638,23 @@
         <v>-10000</v>
       </c>
       <c r="I13" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J13" s="11">
         <v>-50000</v>
       </c>
-      <c r="J13" s="11">
+      <c r="K13" s="11">
         <v>-100000</v>
       </c>
-      <c r="K13" s="11">
+      <c r="L13" s="11">
         <v>-200000</v>
       </c>
-      <c r="L13" s="11">
+      <c r="M13" s="11">
         <v>-500000</v>
       </c>
-      <c r="M13" s="11">
+      <c r="N13" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O13" s="11"/>
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
       <c r="R13" s="11"/>
@@ -5578,8 +5668,9 @@
       <c r="Z13" s="11"/>
       <c r="AA13" s="11"/>
       <c r="AB13" s="11"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC13" s="11"/>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A14" s="11" t="s">
         <v>95</v>
       </c>
@@ -5619,7 +5710,9 @@
       <c r="M14" s="11">
         <v>0</v>
       </c>
-      <c r="O14" s="11"/>
+      <c r="N14" s="11">
+        <v>0</v>
+      </c>
       <c r="P14" s="11"/>
       <c r="Q14" s="11"/>
       <c r="R14" s="11"/>
@@ -5633,8 +5726,9 @@
       <c r="Z14" s="11"/>
       <c r="AA14" s="11"/>
       <c r="AB14" s="11"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC14" s="11"/>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A15" s="11" t="s">
         <v>95</v>
       </c>
@@ -5660,21 +5754,23 @@
         <v>-10000</v>
       </c>
       <c r="I15" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J15" s="11">
         <v>-50000</v>
       </c>
-      <c r="J15" s="11">
+      <c r="K15" s="11">
         <v>-100000</v>
       </c>
-      <c r="K15" s="11">
+      <c r="L15" s="11">
         <v>-200000</v>
       </c>
-      <c r="L15" s="11">
+      <c r="M15" s="11">
         <v>-500000</v>
       </c>
-      <c r="M15" s="11">
+      <c r="N15" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O15" s="11"/>
       <c r="P15" s="11"/>
       <c r="Q15" s="11"/>
       <c r="R15" s="11"/>
@@ -5688,8 +5784,9 @@
       <c r="Z15" s="11"/>
       <c r="AA15" s="11"/>
       <c r="AB15" s="11"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC15" s="11"/>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A16" s="11" t="s">
         <v>95</v>
       </c>
@@ -5715,21 +5812,23 @@
         <v>-10000</v>
       </c>
       <c r="I16" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J16" s="11">
         <v>-50000</v>
       </c>
-      <c r="J16" s="11">
+      <c r="K16" s="11">
         <v>-100000</v>
       </c>
-      <c r="K16" s="11">
+      <c r="L16" s="11">
         <v>-200000</v>
       </c>
-      <c r="L16" s="11">
+      <c r="M16" s="11">
         <v>-500000</v>
       </c>
-      <c r="M16" s="11">
+      <c r="N16" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O16" s="11"/>
       <c r="P16" s="11"/>
       <c r="Q16" s="11"/>
       <c r="R16" s="11"/>
@@ -5743,8 +5842,9 @@
       <c r="Z16" s="11"/>
       <c r="AA16" s="11"/>
       <c r="AB16" s="11"/>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC16" s="11"/>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A17" s="11" t="s">
         <v>147</v>
       </c>
@@ -5784,7 +5884,9 @@
       <c r="M17" s="11">
         <v>0</v>
       </c>
-      <c r="O17" s="11"/>
+      <c r="N17" s="11">
+        <v>0</v>
+      </c>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
       <c r="R17" s="11"/>
@@ -5798,8 +5900,9 @@
       <c r="Z17" s="11"/>
       <c r="AA17" s="11"/>
       <c r="AB17" s="11"/>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC17" s="11"/>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A18" s="11" t="s">
         <v>147</v>
       </c>
@@ -5825,22 +5928,24 @@
         <v>-10000</v>
       </c>
       <c r="I18" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J18" s="11">
         <v>-50000</v>
       </c>
-      <c r="J18" s="11">
+      <c r="K18" s="11">
         <v>-100000</v>
       </c>
-      <c r="K18" s="11">
+      <c r="L18" s="11">
         <v>-200000</v>
       </c>
-      <c r="L18" s="11">
+      <c r="M18" s="11">
         <v>-500000</v>
       </c>
-      <c r="M18" s="11">
+      <c r="N18" s="11">
         <v>-1000000</v>
       </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="11"/>
+      <c r="O18" s="2"/>
       <c r="P18" s="11"/>
       <c r="Q18" s="11"/>
       <c r="R18" s="11"/>
@@ -5854,8 +5959,9 @@
       <c r="Z18" s="11"/>
       <c r="AA18" s="11"/>
       <c r="AB18" s="11"/>
-    </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC18" s="11"/>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A19" s="11" t="s">
         <v>147</v>
       </c>
@@ -5881,21 +5987,23 @@
         <v>-10000</v>
       </c>
       <c r="I19" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J19" s="11">
         <v>-50000</v>
       </c>
-      <c r="J19" s="11">
+      <c r="K19" s="11">
         <v>-100000</v>
       </c>
-      <c r="K19" s="11">
+      <c r="L19" s="11">
         <v>-200000</v>
       </c>
-      <c r="L19" s="11">
+      <c r="M19" s="11">
         <v>-500000</v>
       </c>
-      <c r="M19" s="11">
+      <c r="N19" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O19" s="11"/>
       <c r="P19" s="11"/>
       <c r="Q19" s="11"/>
       <c r="R19" s="11"/>
@@ -5909,8 +6017,9 @@
       <c r="Z19" s="11"/>
       <c r="AA19" s="11"/>
       <c r="AB19" s="11"/>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC19" s="11"/>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A20" s="11" t="s">
         <v>398</v>
       </c>
@@ -5950,7 +6059,9 @@
       <c r="M20" s="11">
         <v>0</v>
       </c>
-      <c r="O20" s="11"/>
+      <c r="N20" s="11">
+        <v>0</v>
+      </c>
       <c r="P20" s="11"/>
       <c r="Q20" s="11"/>
       <c r="R20" s="11"/>
@@ -5964,8 +6075,9 @@
       <c r="Z20" s="11"/>
       <c r="AA20" s="11"/>
       <c r="AB20" s="11"/>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC20" s="11"/>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A21" s="11" t="s">
         <v>398</v>
       </c>
@@ -5991,21 +6103,23 @@
         <v>-10000</v>
       </c>
       <c r="I21" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J21" s="11">
         <v>-50000</v>
       </c>
-      <c r="J21" s="11">
+      <c r="K21" s="11">
         <v>-100000</v>
       </c>
-      <c r="K21" s="11">
+      <c r="L21" s="11">
         <v>-200000</v>
       </c>
-      <c r="L21" s="11">
+      <c r="M21" s="11">
         <v>-500000</v>
       </c>
-      <c r="M21" s="11">
+      <c r="N21" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O21" s="11"/>
       <c r="P21" s="11"/>
       <c r="Q21" s="11"/>
       <c r="R21" s="11"/>
@@ -6019,8 +6133,9 @@
       <c r="Z21" s="11"/>
       <c r="AA21" s="11"/>
       <c r="AB21" s="11"/>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC21" s="11"/>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A22" s="11" t="s">
         <v>398</v>
       </c>
@@ -6046,21 +6161,23 @@
         <v>-10000</v>
       </c>
       <c r="I22" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J22" s="11">
         <v>-50000</v>
       </c>
-      <c r="J22" s="11">
+      <c r="K22" s="11">
         <v>-100000</v>
       </c>
-      <c r="K22" s="11">
+      <c r="L22" s="11">
         <v>-200000</v>
       </c>
-      <c r="L22" s="11">
+      <c r="M22" s="11">
         <v>-500000</v>
       </c>
-      <c r="M22" s="11">
+      <c r="N22" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O22" s="11"/>
       <c r="P22" s="11"/>
       <c r="Q22" s="11"/>
       <c r="R22" s="11"/>
@@ -6074,8 +6191,9 @@
       <c r="Z22" s="11"/>
       <c r="AA22" s="11"/>
       <c r="AB22" s="11"/>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC22" s="11"/>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A23" s="11" t="s">
         <v>399</v>
       </c>
@@ -6115,7 +6233,9 @@
       <c r="M23" s="11">
         <v>0</v>
       </c>
-      <c r="O23" s="11"/>
+      <c r="N23" s="11">
+        <v>0</v>
+      </c>
       <c r="P23" s="11"/>
       <c r="Q23" s="11"/>
       <c r="R23" s="11"/>
@@ -6129,8 +6249,9 @@
       <c r="Z23" s="11"/>
       <c r="AA23" s="11"/>
       <c r="AB23" s="11"/>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC23" s="11"/>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A24" s="11" t="s">
         <v>399</v>
       </c>
@@ -6156,21 +6277,23 @@
         <v>-10000</v>
       </c>
       <c r="I24" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J24" s="11">
         <v>-50000</v>
       </c>
-      <c r="J24" s="11">
+      <c r="K24" s="11">
         <v>-100000</v>
       </c>
-      <c r="K24" s="11">
+      <c r="L24" s="11">
         <v>-200000</v>
       </c>
-      <c r="L24" s="11">
+      <c r="M24" s="11">
         <v>-500000</v>
       </c>
-      <c r="M24" s="11">
+      <c r="N24" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O24" s="11"/>
       <c r="P24" s="11"/>
       <c r="Q24" s="11"/>
       <c r="R24" s="11"/>
@@ -6184,8 +6307,9 @@
       <c r="Z24" s="11"/>
       <c r="AA24" s="11"/>
       <c r="AB24" s="11"/>
-    </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC24" s="11"/>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A25" s="11" t="s">
         <v>399</v>
       </c>
@@ -6211,21 +6335,23 @@
         <v>-10000</v>
       </c>
       <c r="I25" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J25" s="11">
         <v>-50000</v>
       </c>
-      <c r="J25" s="11">
+      <c r="K25" s="11">
         <v>-100000</v>
       </c>
-      <c r="K25" s="11">
+      <c r="L25" s="11">
         <v>-200000</v>
       </c>
-      <c r="L25" s="11">
+      <c r="M25" s="11">
         <v>-500000</v>
       </c>
-      <c r="M25" s="11">
+      <c r="N25" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O25" s="11"/>
       <c r="P25" s="11"/>
       <c r="Q25" s="11"/>
       <c r="R25" s="11"/>
@@ -6239,8 +6365,9 @@
       <c r="Z25" s="11"/>
       <c r="AA25" s="11"/>
       <c r="AB25" s="11"/>
-    </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC25" s="11"/>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A26" s="11" t="s">
         <v>400</v>
       </c>
@@ -6280,7 +6407,9 @@
       <c r="M26" s="11">
         <v>0</v>
       </c>
-      <c r="O26" s="11"/>
+      <c r="N26" s="11">
+        <v>0</v>
+      </c>
       <c r="P26" s="11"/>
       <c r="Q26" s="11"/>
       <c r="R26" s="11"/>
@@ -6294,8 +6423,9 @@
       <c r="Z26" s="11"/>
       <c r="AA26" s="11"/>
       <c r="AB26" s="11"/>
-    </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC26" s="11"/>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A27" s="11" t="s">
         <v>400</v>
       </c>
@@ -6321,21 +6451,23 @@
         <v>-10000</v>
       </c>
       <c r="I27" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J27" s="11">
         <v>-50000</v>
       </c>
-      <c r="J27" s="11">
+      <c r="K27" s="11">
         <v>-100000</v>
       </c>
-      <c r="K27" s="11">
+      <c r="L27" s="11">
         <v>-200000</v>
       </c>
-      <c r="L27" s="11">
+      <c r="M27" s="11">
         <v>-500000</v>
       </c>
-      <c r="M27" s="11">
+      <c r="N27" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O27" s="11"/>
       <c r="P27" s="11"/>
       <c r="Q27" s="11"/>
       <c r="R27" s="11"/>
@@ -6349,8 +6481,9 @@
       <c r="Z27" s="11"/>
       <c r="AA27" s="11"/>
       <c r="AB27" s="11"/>
-    </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC27" s="11"/>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A28" s="11" t="s">
         <v>400</v>
       </c>
@@ -6376,21 +6509,23 @@
         <v>-10000</v>
       </c>
       <c r="I28" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J28" s="11">
         <v>-50000</v>
       </c>
-      <c r="J28" s="11">
+      <c r="K28" s="11">
         <v>-100000</v>
       </c>
-      <c r="K28" s="11">
+      <c r="L28" s="11">
         <v>-200000</v>
       </c>
-      <c r="L28" s="11">
+      <c r="M28" s="11">
         <v>-500000</v>
       </c>
-      <c r="M28" s="11">
+      <c r="N28" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O28" s="11"/>
       <c r="P28" s="11"/>
       <c r="Q28" s="11"/>
       <c r="R28" s="11"/>
@@ -6404,8 +6539,9 @@
       <c r="Z28" s="11"/>
       <c r="AA28" s="11"/>
       <c r="AB28" s="11"/>
-    </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC28" s="11"/>
+    </row>
+    <row r="29" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A29" s="11" t="s">
         <v>401</v>
       </c>
@@ -6445,7 +6581,9 @@
       <c r="M29" s="11">
         <v>0</v>
       </c>
-      <c r="O29" s="11"/>
+      <c r="N29" s="11">
+        <v>0</v>
+      </c>
       <c r="P29" s="11"/>
       <c r="Q29" s="11"/>
       <c r="R29" s="11"/>
@@ -6459,8 +6597,9 @@
       <c r="Z29" s="11"/>
       <c r="AA29" s="11"/>
       <c r="AB29" s="11"/>
-    </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC29" s="11"/>
+    </row>
+    <row r="30" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A30" s="11" t="s">
         <v>401</v>
       </c>
@@ -6486,21 +6625,23 @@
         <v>-10000</v>
       </c>
       <c r="I30" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J30" s="11">
         <v>-50000</v>
       </c>
-      <c r="J30" s="11">
+      <c r="K30" s="11">
         <v>-100000</v>
       </c>
-      <c r="K30" s="11">
+      <c r="L30" s="11">
         <v>-200000</v>
       </c>
-      <c r="L30" s="11">
+      <c r="M30" s="11">
         <v>-500000</v>
       </c>
-      <c r="M30" s="11">
+      <c r="N30" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O30" s="11"/>
       <c r="P30" s="11"/>
       <c r="Q30" s="11"/>
       <c r="R30" s="11"/>
@@ -6514,8 +6655,9 @@
       <c r="Z30" s="11"/>
       <c r="AA30" s="11"/>
       <c r="AB30" s="11"/>
-    </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC30" s="11"/>
+    </row>
+    <row r="31" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A31" s="11" t="s">
         <v>401</v>
       </c>
@@ -6541,21 +6683,23 @@
         <v>-10000</v>
       </c>
       <c r="I31" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J31" s="11">
         <v>-50000</v>
       </c>
-      <c r="J31" s="11">
+      <c r="K31" s="11">
         <v>-100000</v>
       </c>
-      <c r="K31" s="11">
+      <c r="L31" s="11">
         <v>-200000</v>
       </c>
-      <c r="L31" s="11">
+      <c r="M31" s="11">
         <v>-500000</v>
       </c>
-      <c r="M31" s="11">
+      <c r="N31" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O31" s="11"/>
       <c r="P31" s="11"/>
       <c r="Q31" s="11"/>
       <c r="R31" s="11"/>
@@ -6569,8 +6713,9 @@
       <c r="Z31" s="11"/>
       <c r="AA31" s="11"/>
       <c r="AB31" s="11"/>
-    </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC31" s="11"/>
+    </row>
+    <row r="32" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A32" s="11" t="s">
         <v>402</v>
       </c>
@@ -6610,7 +6755,9 @@
       <c r="M32" s="11">
         <v>0</v>
       </c>
-      <c r="O32" s="11"/>
+      <c r="N32" s="11">
+        <v>0</v>
+      </c>
       <c r="P32" s="11"/>
       <c r="Q32" s="11"/>
       <c r="R32" s="11"/>
@@ -6624,8 +6771,9 @@
       <c r="Z32" s="11"/>
       <c r="AA32" s="11"/>
       <c r="AB32" s="11"/>
-    </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AC32" s="11"/>
+    </row>
+    <row r="33" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A33" s="11" t="s">
         <v>402</v>
       </c>
@@ -6651,21 +6799,23 @@
         <v>-10000</v>
       </c>
       <c r="I33" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J33" s="11">
         <v>-50000</v>
       </c>
-      <c r="J33" s="11">
+      <c r="K33" s="11">
         <v>-100000</v>
       </c>
-      <c r="K33" s="11">
+      <c r="L33" s="11">
         <v>-200000</v>
       </c>
-      <c r="L33" s="11">
+      <c r="M33" s="11">
         <v>-500000</v>
       </c>
-      <c r="M33" s="11">
+      <c r="N33" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O33" s="11"/>
       <c r="P33" s="11"/>
       <c r="Q33" s="11"/>
       <c r="R33" s="11"/>
@@ -6679,8 +6829,9 @@
       <c r="Z33" s="11"/>
       <c r="AA33" s="11"/>
       <c r="AB33" s="11"/>
-    </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AC33" s="11"/>
+    </row>
+    <row r="34" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A34" s="11" t="s">
         <v>402</v>
       </c>
@@ -6706,21 +6857,23 @@
         <v>-10000</v>
       </c>
       <c r="I34" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J34" s="11">
         <v>-50000</v>
       </c>
-      <c r="J34" s="11">
+      <c r="K34" s="11">
         <v>-100000</v>
       </c>
-      <c r="K34" s="11">
+      <c r="L34" s="11">
         <v>-200000</v>
       </c>
-      <c r="L34" s="11">
+      <c r="M34" s="11">
         <v>-500000</v>
       </c>
-      <c r="M34" s="11">
+      <c r="N34" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O34" s="11"/>
       <c r="P34" s="11"/>
       <c r="Q34" s="11"/>
       <c r="R34" s="11"/>
@@ -6734,8 +6887,9 @@
       <c r="Z34" s="11"/>
       <c r="AA34" s="11"/>
       <c r="AB34" s="11"/>
-    </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AC34" s="11"/>
+    </row>
+    <row r="35" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A35" s="11" t="s">
         <v>403</v>
       </c>
@@ -6775,7 +6929,9 @@
       <c r="M35" s="11">
         <v>0</v>
       </c>
-      <c r="O35" s="11"/>
+      <c r="N35" s="11">
+        <v>0</v>
+      </c>
       <c r="P35" s="11"/>
       <c r="Q35" s="11"/>
       <c r="R35" s="11"/>
@@ -6790,8 +6946,9 @@
       <c r="AA35" s="11"/>
       <c r="AB35" s="11"/>
       <c r="AC35" s="11"/>
-    </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AD35" s="11"/>
+    </row>
+    <row r="36" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A36" s="11" t="s">
         <v>403</v>
       </c>
@@ -6817,21 +6974,23 @@
         <v>-10000</v>
       </c>
       <c r="I36" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J36" s="11">
         <v>-50000</v>
       </c>
-      <c r="J36" s="11">
+      <c r="K36" s="11">
         <v>-100000</v>
       </c>
-      <c r="K36" s="11">
+      <c r="L36" s="11">
         <v>-200000</v>
       </c>
-      <c r="L36" s="11">
+      <c r="M36" s="11">
         <v>-500000</v>
       </c>
-      <c r="M36" s="11">
+      <c r="N36" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O36" s="11"/>
       <c r="P36" s="11"/>
       <c r="Q36" s="11"/>
       <c r="R36" s="11"/>
@@ -6846,8 +7005,9 @@
       <c r="AA36" s="11"/>
       <c r="AB36" s="11"/>
       <c r="AC36" s="11"/>
-    </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AD36" s="11"/>
+    </row>
+    <row r="37" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A37" s="11" t="s">
         <v>403</v>
       </c>
@@ -6873,21 +7033,23 @@
         <v>-10000</v>
       </c>
       <c r="I37" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J37" s="11">
         <v>-50000</v>
       </c>
-      <c r="J37" s="11">
+      <c r="K37" s="11">
         <v>-100000</v>
       </c>
-      <c r="K37" s="11">
+      <c r="L37" s="11">
         <v>-200000</v>
       </c>
-      <c r="L37" s="11">
+      <c r="M37" s="11">
         <v>-500000</v>
       </c>
-      <c r="M37" s="11">
+      <c r="N37" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O37" s="11"/>
       <c r="P37" s="11"/>
       <c r="Q37" s="11"/>
       <c r="R37" s="11"/>
@@ -6902,8 +7064,9 @@
       <c r="AA37" s="11"/>
       <c r="AB37" s="11"/>
       <c r="AC37" s="11"/>
-    </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AD37" s="11"/>
+    </row>
+    <row r="38" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A38" s="11" t="s">
         <v>404</v>
       </c>
@@ -6943,7 +7106,9 @@
       <c r="M38" s="11">
         <v>0</v>
       </c>
-      <c r="O38" s="11"/>
+      <c r="N38" s="11">
+        <v>0</v>
+      </c>
       <c r="P38" s="11"/>
       <c r="Q38" s="11"/>
       <c r="R38" s="11"/>
@@ -6957,8 +7122,9 @@
       <c r="Z38" s="11"/>
       <c r="AA38" s="11"/>
       <c r="AB38" s="11"/>
-    </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AC38" s="11"/>
+    </row>
+    <row r="39" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A39" s="11" t="s">
         <v>404</v>
       </c>
@@ -6984,21 +7150,23 @@
         <v>-10000</v>
       </c>
       <c r="I39" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J39" s="11">
         <v>-50000</v>
       </c>
-      <c r="J39" s="11">
+      <c r="K39" s="11">
         <v>-100000</v>
       </c>
-      <c r="K39" s="11">
+      <c r="L39" s="11">
         <v>-200000</v>
       </c>
-      <c r="L39" s="11">
+      <c r="M39" s="11">
         <v>-500000</v>
       </c>
-      <c r="M39" s="11">
+      <c r="N39" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O39" s="11"/>
       <c r="P39" s="11"/>
       <c r="Q39" s="11"/>
       <c r="R39" s="11"/>
@@ -7012,8 +7180,9 @@
       <c r="Z39" s="11"/>
       <c r="AA39" s="11"/>
       <c r="AB39" s="11"/>
-    </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AC39" s="11"/>
+    </row>
+    <row r="40" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A40" s="11" t="s">
         <v>404</v>
       </c>
@@ -7039,21 +7208,23 @@
         <v>-10000</v>
       </c>
       <c r="I40" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J40" s="11">
         <v>-50000</v>
       </c>
-      <c r="J40" s="11">
+      <c r="K40" s="11">
         <v>-100000</v>
       </c>
-      <c r="K40" s="11">
+      <c r="L40" s="11">
         <v>-200000</v>
       </c>
-      <c r="L40" s="11">
+      <c r="M40" s="11">
         <v>-500000</v>
       </c>
-      <c r="M40" s="11">
+      <c r="N40" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O40" s="11"/>
       <c r="P40" s="11"/>
       <c r="Q40" s="11"/>
       <c r="R40" s="11"/>
@@ -7067,8 +7238,9 @@
       <c r="Z40" s="11"/>
       <c r="AA40" s="11"/>
       <c r="AB40" s="11"/>
-    </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AC40" s="11"/>
+    </row>
+    <row r="41" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A41" s="11" t="s">
         <v>405</v>
       </c>
@@ -7108,7 +7280,9 @@
       <c r="M41" s="11">
         <v>0</v>
       </c>
-      <c r="O41" s="11"/>
+      <c r="N41" s="11">
+        <v>0</v>
+      </c>
       <c r="P41" s="11"/>
       <c r="Q41" s="11"/>
       <c r="R41" s="11"/>
@@ -7122,8 +7296,9 @@
       <c r="Z41" s="11"/>
       <c r="AA41" s="11"/>
       <c r="AB41" s="11"/>
-    </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AC41" s="11"/>
+    </row>
+    <row r="42" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A42" s="11" t="s">
         <v>405</v>
       </c>
@@ -7149,21 +7324,23 @@
         <v>-10000</v>
       </c>
       <c r="I42" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J42" s="11">
         <v>-50000</v>
       </c>
-      <c r="J42" s="11">
+      <c r="K42" s="11">
         <v>-100000</v>
       </c>
-      <c r="K42" s="11">
+      <c r="L42" s="11">
         <v>-200000</v>
       </c>
-      <c r="L42" s="11">
+      <c r="M42" s="11">
         <v>-500000</v>
       </c>
-      <c r="M42" s="11">
+      <c r="N42" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O42" s="11"/>
       <c r="P42" s="11"/>
       <c r="Q42" s="11"/>
       <c r="R42" s="11"/>
@@ -7177,8 +7354,9 @@
       <c r="Z42" s="11"/>
       <c r="AA42" s="11"/>
       <c r="AB42" s="11"/>
-    </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AC42" s="11"/>
+    </row>
+    <row r="43" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A43" s="11" t="s">
         <v>405</v>
       </c>
@@ -7204,21 +7382,23 @@
         <v>-10000</v>
       </c>
       <c r="I43" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J43" s="11">
         <v>-50000</v>
       </c>
-      <c r="J43" s="11">
+      <c r="K43" s="11">
         <v>-100000</v>
       </c>
-      <c r="K43" s="11">
+      <c r="L43" s="11">
         <v>-200000</v>
       </c>
-      <c r="L43" s="11">
+      <c r="M43" s="11">
         <v>-500000</v>
       </c>
-      <c r="M43" s="11">
+      <c r="N43" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O43" s="11"/>
       <c r="P43" s="11"/>
       <c r="Q43" s="11"/>
       <c r="R43" s="11"/>
@@ -7232,8 +7412,9 @@
       <c r="Z43" s="11"/>
       <c r="AA43" s="11"/>
       <c r="AB43" s="11"/>
-    </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AC43" s="11"/>
+    </row>
+    <row r="44" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A44" s="11" t="s">
         <v>406</v>
       </c>
@@ -7273,7 +7454,9 @@
       <c r="M44" s="11">
         <v>0</v>
       </c>
-      <c r="O44" s="11"/>
+      <c r="N44" s="11">
+        <v>0</v>
+      </c>
       <c r="P44" s="11"/>
       <c r="Q44" s="11"/>
       <c r="R44" s="11"/>
@@ -7287,8 +7470,9 @@
       <c r="Z44" s="11"/>
       <c r="AA44" s="11"/>
       <c r="AB44" s="11"/>
-    </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AC44" s="11"/>
+    </row>
+    <row r="45" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A45" s="11" t="s">
         <v>406</v>
       </c>
@@ -7314,21 +7498,23 @@
         <v>-10000</v>
       </c>
       <c r="I45" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J45" s="11">
         <v>-50000</v>
       </c>
-      <c r="J45" s="11">
+      <c r="K45" s="11">
         <v>-100000</v>
       </c>
-      <c r="K45" s="11">
+      <c r="L45" s="11">
         <v>-200000</v>
       </c>
-      <c r="L45" s="11">
+      <c r="M45" s="11">
         <v>-500000</v>
       </c>
-      <c r="M45" s="11">
+      <c r="N45" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O45" s="11"/>
       <c r="P45" s="11"/>
       <c r="Q45" s="11"/>
       <c r="R45" s="11"/>
@@ -7342,8 +7528,9 @@
       <c r="Z45" s="11"/>
       <c r="AA45" s="11"/>
       <c r="AB45" s="11"/>
-    </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AC45" s="11"/>
+    </row>
+    <row r="46" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A46" s="11" t="s">
         <v>406</v>
       </c>
@@ -7369,21 +7556,23 @@
         <v>-10000</v>
       </c>
       <c r="I46" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J46" s="11">
         <v>-50000</v>
       </c>
-      <c r="J46" s="11">
+      <c r="K46" s="11">
         <v>-100000</v>
       </c>
-      <c r="K46" s="11">
+      <c r="L46" s="11">
         <v>-200000</v>
       </c>
-      <c r="L46" s="11">
+      <c r="M46" s="11">
         <v>-500000</v>
       </c>
-      <c r="M46" s="11">
+      <c r="N46" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O46" s="11"/>
       <c r="P46" s="11"/>
       <c r="Q46" s="11"/>
       <c r="R46" s="11"/>
@@ -7397,42 +7586,43 @@
       <c r="Z46" s="11"/>
       <c r="AA46" s="11"/>
       <c r="AB46" s="11"/>
-    </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AC46" s="11"/>
+    </row>
+    <row r="47" spans="1:30" x14ac:dyDescent="0.45">
       <c r="E47" s="11"/>
       <c r="G47" s="11"/>
       <c r="H47" s="11"/>
-      <c r="I47" s="11"/>
-      <c r="K47" s="11"/>
+      <c r="J47" s="11"/>
       <c r="L47" s="11"/>
       <c r="M47" s="11"/>
-    </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="N47" s="11"/>
+    </row>
+    <row r="48" spans="1:30" x14ac:dyDescent="0.45">
       <c r="E48" s="11"/>
       <c r="G48" s="11"/>
       <c r="H48" s="11"/>
-      <c r="I48" s="11"/>
-      <c r="K48" s="11"/>
+      <c r="J48" s="11"/>
       <c r="L48" s="11"/>
       <c r="M48" s="11"/>
-    </row>
-    <row r="49" spans="5:13" x14ac:dyDescent="0.45">
+      <c r="N48" s="11"/>
+    </row>
+    <row r="49" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E49" s="11"/>
       <c r="G49" s="11"/>
       <c r="H49" s="11"/>
-      <c r="I49" s="11"/>
-      <c r="K49" s="11"/>
+      <c r="J49" s="11"/>
       <c r="L49" s="11"/>
       <c r="M49" s="11"/>
-    </row>
-    <row r="51" spans="5:13" x14ac:dyDescent="0.45">
+      <c r="N49" s="11"/>
+    </row>
+    <row r="51" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E51" s="11"/>
       <c r="G51" s="11"/>
       <c r="H51" s="11"/>
-      <c r="I51" s="11"/>
-      <c r="K51" s="11"/>
+      <c r="J51" s="11"/>
       <c r="L51" s="11"/>
       <c r="M51" s="11"/>
+      <c r="N51" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -7462,7 +7652,7 @@
         <v>264</v>
       </c>
       <c r="B2" s="17">
-        <v>-5</v>
+        <v>-2.7777777777777781</v>
       </c>
       <c r="C2" s="17"/>
       <c r="D2" s="17"/>
@@ -7504,7 +7694,7 @@
         <v>265</v>
       </c>
       <c r="B3" s="17">
-        <v>-51</v>
+        <v>-28.333333333333332</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
@@ -7541,7 +7731,7 @@
         <v>266</v>
       </c>
       <c r="B4" s="17">
-        <v>-512</v>
+        <v>-284.44444444444446</v>
       </c>
       <c r="C4" s="17"/>
       <c r="D4" s="17"/>
@@ -7583,7 +7773,7 @@
         <v>267</v>
       </c>
       <c r="B5" s="17">
-        <v>-5114</v>
+        <v>-2841.1111111111113</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="17"/>
@@ -7620,7 +7810,7 @@
         <v>125</v>
       </c>
       <c r="B6" s="17">
-        <v>-50376</v>
+        <v>-27986.666666666668</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
@@ -7662,7 +7852,7 @@
         <v>268</v>
       </c>
       <c r="B7" s="17">
-        <v>-6</v>
+        <v>-3.3333333333333335</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
@@ -7704,7 +7894,7 @@
         <v>269</v>
       </c>
       <c r="B8" s="17">
-        <v>-53</v>
+        <v>-29.444444444444443</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
@@ -7741,7 +7931,7 @@
         <v>270</v>
       </c>
       <c r="B9" s="17">
-        <v>-514</v>
+        <v>-285.55555555555554</v>
       </c>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
@@ -7783,7 +7973,7 @@
         <v>271</v>
       </c>
       <c r="B10" s="17">
-        <v>-5116</v>
+        <v>-2842.2222222222217</v>
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="17"/>
@@ -7820,7 +8010,7 @@
         <v>126</v>
       </c>
       <c r="B11" s="17">
-        <v>-50367</v>
+        <v>-27981.666666666668</v>
       </c>
       <c r="C11" s="17"/>
       <c r="D11" s="17"/>
@@ -7862,7 +8052,7 @@
         <v>272</v>
       </c>
       <c r="B12" s="17">
-        <v>-9</v>
+        <v>-5</v>
       </c>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
@@ -7876,7 +8066,7 @@
         <v>273</v>
       </c>
       <c r="B13" s="17">
-        <v>-62</v>
+        <v>-34.444444444444443</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
@@ -7890,7 +8080,7 @@
         <v>274</v>
       </c>
       <c r="B14" s="17">
-        <v>-529</v>
+        <v>-293.88888888888886</v>
       </c>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
@@ -7904,7 +8094,7 @@
         <v>275</v>
       </c>
       <c r="B15" s="17">
-        <v>-5132</v>
+        <v>-2851.1111111111113</v>
       </c>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
@@ -7918,7 +8108,7 @@
         <v>276</v>
       </c>
       <c r="B16" s="17">
-        <v>-50257</v>
+        <v>-27920.555555555558</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
@@ -7932,7 +8122,7 @@
         <v>291</v>
       </c>
       <c r="B17" s="17">
-        <v>-16</v>
+        <v>-8.8888888888888893</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
@@ -7946,7 +8136,7 @@
         <v>292</v>
       </c>
       <c r="B18" s="17">
-        <v>-88</v>
+        <v>-48.888888888888886</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
@@ -7960,7 +8150,7 @@
         <v>293</v>
       </c>
       <c r="B19" s="17">
-        <v>-616</v>
+        <v>-342.22222222222229</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
@@ -7974,7 +8164,7 @@
         <v>294</v>
       </c>
       <c r="B20" s="17">
-        <v>-5283</v>
+        <v>-2935</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
@@ -7988,7 +8178,7 @@
         <v>295</v>
       </c>
       <c r="B21" s="17">
-        <v>-46061</v>
+        <v>-25589.444444444442</v>
       </c>
       <c r="C21" s="17"/>
       <c r="D21" s="17"/>
@@ -8002,7 +8192,7 @@
         <v>240</v>
       </c>
       <c r="B22" s="17">
-        <v>-41</v>
+        <v>-22.777777777777775</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
@@ -8016,7 +8206,7 @@
         <v>241</v>
       </c>
       <c r="B23" s="17">
-        <v>-156</v>
+        <v>-86.666666666666671</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
@@ -8030,7 +8220,7 @@
         <v>242</v>
       </c>
       <c r="B24" s="17">
-        <v>-877</v>
+        <v>-487.22222222222229</v>
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
@@ -8044,7 +8234,7 @@
         <v>243</v>
       </c>
       <c r="B25" s="17">
-        <v>-6156</v>
+        <v>-3420</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="17"/>
@@ -8058,7 +8248,7 @@
         <v>244</v>
       </c>
       <c r="B26" s="17">
-        <v>-47658</v>
+        <v>-26476.666666666668</v>
       </c>
       <c r="C26" s="17"/>
       <c r="D26" s="17"/>
@@ -8072,7 +8262,7 @@
         <v>296</v>
       </c>
       <c r="B27" s="17">
-        <v>-179</v>
+        <v>-99.444444444444429</v>
       </c>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
@@ -8086,7 +8276,7 @@
         <v>297</v>
       </c>
       <c r="B28" s="17">
-        <v>-413</v>
+        <v>-229.44444444444446</v>
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
@@ -8100,7 +8290,7 @@
         <v>298</v>
       </c>
       <c r="B29" s="17">
-        <v>-1562</v>
+        <v>-867.77777777777783</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
@@ -8114,7 +8304,7 @@
         <v>299</v>
       </c>
       <c r="B30" s="17">
-        <v>-8763</v>
+        <v>-4868.333333333333</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
@@ -8128,7 +8318,7 @@
         <v>300</v>
       </c>
       <c r="B31" s="17">
-        <v>-60612</v>
+        <v>-33673.333333333336</v>
       </c>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
@@ -8142,7 +8332,7 @@
         <v>245</v>
       </c>
       <c r="B32" s="17">
-        <v>-631</v>
+        <v>-350.5555555555556</v>
       </c>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
@@ -8156,7 +8346,7 @@
         <v>246</v>
       </c>
       <c r="B33" s="17">
-        <v>-1733</v>
+        <v>-962.77777777777783</v>
       </c>
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
@@ -8170,7 +8360,7 @@
         <v>247</v>
       </c>
       <c r="B34" s="17">
-        <v>-4045</v>
+        <v>-2247.2222222222222</v>
       </c>
       <c r="C34" s="17"/>
       <c r="D34" s="17"/>
@@ -8184,7 +8374,7 @@
         <v>248</v>
       </c>
       <c r="B35" s="17">
-        <v>-15449</v>
+        <v>-8582.7777777777774</v>
       </c>
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
@@ -8198,7 +8388,7 @@
         <v>249</v>
       </c>
       <c r="B36" s="17">
-        <v>-86973</v>
+        <v>-48318.333333333336</v>
       </c>
       <c r="C36" s="17"/>
       <c r="D36" s="17"/>

--- a/templates/3D/sust yield server/setup.xlsx
+++ b/templates/3D/sust yield server/setup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B641C5A-12B4-4CA8-9971-CE19F5130DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F928BB2A-1145-4D23-9B85-DDBC27CD0ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="2" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grid" sheetId="1" r:id="rId1"/>
@@ -7652,7 +7652,7 @@
         <v>264</v>
       </c>
       <c r="B2" s="17">
-        <v>-2.7777777777777781</v>
+        <v>-3</v>
       </c>
       <c r="C2" s="17"/>
       <c r="D2" s="17"/>
@@ -7694,7 +7694,7 @@
         <v>265</v>
       </c>
       <c r="B3" s="17">
-        <v>-28.333333333333332</v>
+        <v>-28</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
@@ -7731,7 +7731,7 @@
         <v>266</v>
       </c>
       <c r="B4" s="17">
-        <v>-284.44444444444446</v>
+        <v>-284</v>
       </c>
       <c r="C4" s="17"/>
       <c r="D4" s="17"/>
@@ -7773,7 +7773,7 @@
         <v>267</v>
       </c>
       <c r="B5" s="17">
-        <v>-2841.1111111111113</v>
+        <v>-2841</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="17"/>
@@ -7810,7 +7810,7 @@
         <v>125</v>
       </c>
       <c r="B6" s="17">
-        <v>-27986.666666666668</v>
+        <v>-27987</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
@@ -7852,7 +7852,7 @@
         <v>268</v>
       </c>
       <c r="B7" s="17">
-        <v>-3.3333333333333335</v>
+        <v>-3</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
@@ -7894,7 +7894,7 @@
         <v>269</v>
       </c>
       <c r="B8" s="17">
-        <v>-29.444444444444443</v>
+        <v>-29</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
@@ -7931,7 +7931,7 @@
         <v>270</v>
       </c>
       <c r="B9" s="17">
-        <v>-285.55555555555554</v>
+        <v>-286</v>
       </c>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
@@ -7973,7 +7973,7 @@
         <v>271</v>
       </c>
       <c r="B10" s="17">
-        <v>-2842.2222222222217</v>
+        <v>-2842</v>
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="17"/>
@@ -8010,7 +8010,7 @@
         <v>126</v>
       </c>
       <c r="B11" s="17">
-        <v>-27981.666666666668</v>
+        <v>-27982</v>
       </c>
       <c r="C11" s="17"/>
       <c r="D11" s="17"/>
@@ -8066,7 +8066,7 @@
         <v>273</v>
       </c>
       <c r="B13" s="17">
-        <v>-34.444444444444443</v>
+        <v>-34</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
@@ -8080,7 +8080,7 @@
         <v>274</v>
       </c>
       <c r="B14" s="17">
-        <v>-293.88888888888886</v>
+        <v>-294</v>
       </c>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
@@ -8094,7 +8094,7 @@
         <v>275</v>
       </c>
       <c r="B15" s="17">
-        <v>-2851.1111111111113</v>
+        <v>-2851</v>
       </c>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
@@ -8108,7 +8108,7 @@
         <v>276</v>
       </c>
       <c r="B16" s="17">
-        <v>-27920.555555555558</v>
+        <v>-27921</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
@@ -8122,7 +8122,7 @@
         <v>291</v>
       </c>
       <c r="B17" s="17">
-        <v>-8.8888888888888893</v>
+        <v>-9</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
@@ -8136,7 +8136,7 @@
         <v>292</v>
       </c>
       <c r="B18" s="17">
-        <v>-48.888888888888886</v>
+        <v>-49</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
@@ -8150,7 +8150,7 @@
         <v>293</v>
       </c>
       <c r="B19" s="17">
-        <v>-342.22222222222229</v>
+        <v>-342</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
@@ -8178,7 +8178,7 @@
         <v>295</v>
       </c>
       <c r="B21" s="17">
-        <v>-25589.444444444442</v>
+        <v>-25589</v>
       </c>
       <c r="C21" s="17"/>
       <c r="D21" s="17"/>
@@ -8192,7 +8192,7 @@
         <v>240</v>
       </c>
       <c r="B22" s="17">
-        <v>-22.777777777777775</v>
+        <v>-23</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
@@ -8206,7 +8206,7 @@
         <v>241</v>
       </c>
       <c r="B23" s="17">
-        <v>-86.666666666666671</v>
+        <v>-87</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
@@ -8220,7 +8220,7 @@
         <v>242</v>
       </c>
       <c r="B24" s="17">
-        <v>-487.22222222222229</v>
+        <v>-487</v>
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
@@ -8248,7 +8248,7 @@
         <v>244</v>
       </c>
       <c r="B26" s="17">
-        <v>-26476.666666666668</v>
+        <v>-26477</v>
       </c>
       <c r="C26" s="17"/>
       <c r="D26" s="17"/>
@@ -8262,7 +8262,7 @@
         <v>296</v>
       </c>
       <c r="B27" s="17">
-        <v>-99.444444444444429</v>
+        <v>-99</v>
       </c>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
@@ -8276,7 +8276,7 @@
         <v>297</v>
       </c>
       <c r="B28" s="17">
-        <v>-229.44444444444446</v>
+        <v>-229</v>
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
@@ -8290,7 +8290,7 @@
         <v>298</v>
       </c>
       <c r="B29" s="17">
-        <v>-867.77777777777783</v>
+        <v>-868</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
@@ -8304,7 +8304,7 @@
         <v>299</v>
       </c>
       <c r="B30" s="17">
-        <v>-4868.333333333333</v>
+        <v>-4868</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
@@ -8318,7 +8318,7 @@
         <v>300</v>
       </c>
       <c r="B31" s="17">
-        <v>-33673.333333333336</v>
+        <v>-33673</v>
       </c>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
@@ -8332,7 +8332,7 @@
         <v>245</v>
       </c>
       <c r="B32" s="17">
-        <v>-350.5555555555556</v>
+        <v>-351</v>
       </c>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
@@ -8346,7 +8346,7 @@
         <v>246</v>
       </c>
       <c r="B33" s="17">
-        <v>-962.77777777777783</v>
+        <v>-963</v>
       </c>
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
@@ -8360,7 +8360,7 @@
         <v>247</v>
       </c>
       <c r="B34" s="17">
-        <v>-2247.2222222222222</v>
+        <v>-2247</v>
       </c>
       <c r="C34" s="17"/>
       <c r="D34" s="17"/>
@@ -8374,7 +8374,7 @@
         <v>248</v>
       </c>
       <c r="B35" s="17">
-        <v>-8582.7777777777774</v>
+        <v>-8583</v>
       </c>
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
@@ -8388,7 +8388,7 @@
         <v>249</v>
       </c>
       <c r="B36" s="17">
-        <v>-48318.333333333336</v>
+        <v>-48318</v>
       </c>
       <c r="C36" s="17"/>
       <c r="D36" s="17"/>
